--- a/NIFTY_100_Technical_Metrics.xlsx
+++ b/NIFTY_100_Technical_Metrics.xlsx
@@ -1797,7 +1797,7 @@
         <v>94</v>
       </c>
       <c r="P2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q2">
         <v>6914.5</v>
@@ -1913,7 +1913,7 @@
         <v>81</v>
       </c>
       <c r="P3">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q3">
         <v>1307.16</v>
@@ -2029,7 +2029,7 @@
         <v>42</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q4">
         <v>2737.46</v>
@@ -2145,7 +2145,7 @@
         <v>71</v>
       </c>
       <c r="P5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q5">
         <v>1285.98</v>
@@ -2261,7 +2261,7 @@
         <v>92</v>
       </c>
       <c r="P6">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q6">
         <v>1755.3</v>
@@ -2377,7 +2377,7 @@
         <v>78</v>
       </c>
       <c r="P7">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q7">
         <v>195.47</v>
@@ -2493,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q8">
         <v>355.49</v>
@@ -2609,7 +2609,7 @@
         <v>60</v>
       </c>
       <c r="P9">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q9">
         <v>7902</v>
@@ -2725,7 +2725,7 @@
         <v>47</v>
       </c>
       <c r="P10">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q10">
         <v>2362.6</v>
@@ -2841,7 +2841,7 @@
         <v>72</v>
       </c>
       <c r="P11">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q11">
         <v>1243.36</v>
@@ -3073,7 +3073,7 @@
         <v>28</v>
       </c>
       <c r="P13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q13">
         <v>1737.96</v>
@@ -3189,7 +3189,7 @@
         <v>61</v>
       </c>
       <c r="P14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q14">
         <v>10682.8</v>
@@ -3305,7 +3305,7 @@
         <v>48</v>
       </c>
       <c r="P15">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q15">
         <v>962.58</v>
@@ -3421,7 +3421,7 @@
         <v>49</v>
       </c>
       <c r="P16">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q16">
         <v>233.98</v>
@@ -3537,7 +3537,7 @@
         <v>30</v>
       </c>
       <c r="P17">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q17">
         <v>377.2</v>
@@ -3769,7 +3769,7 @@
         <v>87</v>
       </c>
       <c r="P19">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q19">
         <v>44214</v>
@@ -3885,7 +3885,7 @@
         <v>40</v>
       </c>
       <c r="P20">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q20">
         <v>293.57</v>
@@ -4001,7 +4001,7 @@
         <v>25</v>
       </c>
       <c r="P21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q21">
         <v>4800.88</v>
@@ -4117,7 +4117,7 @@
         <v>54</v>
       </c>
       <c r="P22">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q22">
         <v>118.48</v>
@@ -4233,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="P23">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q23">
         <v>881.28</v>
@@ -4349,7 +4349,7 @@
         <v>41</v>
       </c>
       <c r="P24">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q24">
         <v>1582.54</v>
@@ -4465,7 +4465,7 @@
         <v>33</v>
       </c>
       <c r="P25">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q25">
         <v>1322.14</v>
@@ -4581,7 +4581,7 @@
         <v>80</v>
       </c>
       <c r="P26">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q26">
         <v>414.43</v>
@@ -4697,7 +4697,7 @@
         <v>79</v>
       </c>
       <c r="P27">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q27">
         <v>4838.88</v>
@@ -4929,7 +4929,7 @@
         <v>43</v>
       </c>
       <c r="P29">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q29">
         <v>656.13</v>
@@ -5045,7 +5045,7 @@
         <v>23</v>
       </c>
       <c r="P30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q30">
         <v>3577.34</v>
@@ -5161,7 +5161,7 @@
         <v>65</v>
       </c>
       <c r="P31">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q31">
         <v>1198.36</v>
@@ -5277,7 +5277,7 @@
         <v>63</v>
       </c>
       <c r="P32">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q32">
         <v>6970</v>
@@ -5393,7 +5393,7 @@
         <v>46</v>
       </c>
       <c r="P33">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Q33">
         <v>3249.78</v>
@@ -5509,7 +5509,7 @@
         <v>83</v>
       </c>
       <c r="P34">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q34">
         <v>324.06</v>
@@ -5625,7 +5625,7 @@
         <v>57</v>
       </c>
       <c r="P35">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q35">
         <v>168.93</v>
@@ -5741,7 +5741,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q36">
         <v>860.11</v>
@@ -5857,7 +5857,7 @@
         <v>51</v>
       </c>
       <c r="P37">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q37">
         <v>2921.78</v>
@@ -6089,7 +6089,7 @@
         <v>59</v>
       </c>
       <c r="P39">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q39">
         <v>1196.98</v>
@@ -6205,7 +6205,7 @@
         <v>16</v>
       </c>
       <c r="P40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q40">
         <v>2304.14</v>
@@ -6321,7 +6321,7 @@
         <v>13</v>
       </c>
       <c r="P41">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q41">
         <v>703.7</v>
@@ -6437,7 +6437,7 @@
         <v>32</v>
       </c>
       <c r="P42">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q42">
         <v>544.4299999999999</v>
@@ -6553,7 +6553,7 @@
         <v>76</v>
       </c>
       <c r="P43">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q43">
         <v>916.05</v>
@@ -6785,7 +6785,7 @@
         <v>86</v>
       </c>
       <c r="P45">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q45">
         <v>548.97</v>
@@ -7133,7 +7133,7 @@
         <v>64</v>
       </c>
       <c r="P48">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q48">
         <v>723.92</v>
@@ -7249,7 +7249,7 @@
         <v>35</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q49">
         <v>4924.32</v>
@@ -7365,7 +7365,7 @@
         <v>22</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q50">
         <v>1009.35</v>
@@ -7481,7 +7481,7 @@
         <v>31</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q51">
         <v>128.94</v>
@@ -7597,7 +7597,7 @@
         <v>4</v>
       </c>
       <c r="P52">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q52">
         <v>75.75</v>
@@ -7713,7 +7713,7 @@
         <v>20</v>
       </c>
       <c r="P53">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q53">
         <v>264.46</v>
@@ -7829,7 +7829,7 @@
         <v>52</v>
       </c>
       <c r="P54">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q54">
         <v>1054.18</v>
@@ -7945,7 +7945,7 @@
         <v>9</v>
       </c>
       <c r="P55">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q55">
         <v>214.39</v>
@@ -8061,7 +8061,7 @@
         <v>56</v>
       </c>
       <c r="P56">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q56">
         <v>1213.62</v>
@@ -8177,7 +8177,7 @@
         <v>91</v>
       </c>
       <c r="P57">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q57">
         <v>432.78</v>
@@ -8293,7 +8293,7 @@
         <v>37</v>
       </c>
       <c r="P58">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q58">
         <v>1101.58</v>
@@ -8409,7 +8409,7 @@
         <v>58</v>
       </c>
       <c r="P59">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q59">
         <v>3709.98</v>
@@ -8525,7 +8525,7 @@
         <v>36</v>
       </c>
       <c r="P60">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q60">
         <v>3979.22</v>
@@ -8757,7 +8757,7 @@
         <v>6</v>
       </c>
       <c r="P62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q62">
         <v>11451</v>
@@ -8873,7 +8873,7 @@
         <v>7</v>
       </c>
       <c r="P63">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q63">
         <v>896.9400000000001</v>
@@ -9105,7 +9105,7 @@
         <v>98</v>
       </c>
       <c r="P65">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q65">
         <v>156.36</v>
@@ -9221,7 +9221,7 @@
         <v>17</v>
       </c>
       <c r="P66">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q66">
         <v>2648.22</v>
@@ -9453,7 +9453,7 @@
         <v>44</v>
       </c>
       <c r="P68">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q68">
         <v>316.34</v>
@@ -9569,7 +9569,7 @@
         <v>45</v>
       </c>
       <c r="P69">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q69">
         <v>222.41</v>
@@ -9801,7 +9801,7 @@
         <v>55</v>
       </c>
       <c r="P71">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q71">
         <v>1487.76</v>
@@ -9917,7 +9917,7 @@
         <v>89</v>
       </c>
       <c r="P72">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q72">
         <v>114.23</v>
@@ -10033,7 +10033,7 @@
         <v>34</v>
       </c>
       <c r="P73">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q73">
         <v>252.21</v>
@@ -10149,7 +10149,7 @@
         <v>21</v>
       </c>
       <c r="P74">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q74">
         <v>297.91</v>
@@ -10265,7 +10265,7 @@
         <v>27</v>
       </c>
       <c r="P75">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q75">
         <v>1192.08</v>
@@ -10381,7 +10381,7 @@
         <v>50</v>
       </c>
       <c r="P76">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q76">
         <v>1710.54</v>
@@ -10497,7 +10497,7 @@
         <v>74</v>
       </c>
       <c r="P77">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q77">
         <v>953.97</v>
@@ -10613,7 +10613,7 @@
         <v>11</v>
       </c>
       <c r="P78">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q78">
         <v>21932</v>
@@ -10729,7 +10729,7 @@
         <v>95</v>
       </c>
       <c r="P79">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q79">
         <v>948.4299999999999</v>
@@ -10845,7 +10845,7 @@
         <v>84</v>
       </c>
       <c r="P80">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q80">
         <v>3716.42</v>
@@ -10961,7 +10961,7 @@
         <v>97</v>
       </c>
       <c r="P81">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q81">
         <v>19906.2</v>
@@ -11300,7 +11300,7 @@
         <v>24</v>
       </c>
       <c r="P84">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q84">
         <v>961.03</v>
@@ -11416,7 +11416,7 @@
         <v>29</v>
       </c>
       <c r="P85">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q85">
         <v>345.22</v>
@@ -11532,7 +11532,7 @@
         <v>62</v>
       </c>
       <c r="P86">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q86">
         <v>175.65</v>
@@ -11648,7 +11648,7 @@
         <v>38</v>
       </c>
       <c r="P87">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q87">
         <v>2105.34</v>
@@ -11880,7 +11880,7 @@
         <v>90</v>
       </c>
       <c r="P89">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q89">
         <v>4455.3</v>
@@ -12103,7 +12103,7 @@
         <v>2</v>
       </c>
       <c r="P91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q91">
         <v>282.07</v>
@@ -12335,7 +12335,7 @@
         <v>18</v>
       </c>
       <c r="P93">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q93">
         <v>2834.16</v>
@@ -12567,7 +12567,7 @@
         <v>39</v>
       </c>
       <c r="P95">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q95">
         <v>10671.8</v>
@@ -12799,7 +12799,7 @@
         <v>69</v>
       </c>
       <c r="P97">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q97">
         <v>1351.04</v>
@@ -12915,7 +12915,7 @@
         <v>70</v>
       </c>
       <c r="P98">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q98">
         <v>438.53</v>
@@ -13031,7 +13031,7 @@
         <v>8</v>
       </c>
       <c r="P99">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q99">
         <v>259.83</v>
@@ -13147,7 +13147,7 @@
         <v>14</v>
       </c>
       <c r="P100">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q100">
         <v>160.91</v>
@@ -13263,7 +13263,7 @@
         <v>82</v>
       </c>
       <c r="P101">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q101">
         <v>1136.2</v>
